--- a/btc_history.xlsx
+++ b/btc_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -483,6 +483,27 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:56 UTC</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>76011</v>
+      </c>
+      <c r="C3" t="n">
+        <v>111510927</v>
+      </c>
+      <c r="D3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/btc_history.xlsx
+++ b/btc_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -504,6 +504,27 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:20 UTC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>76101</v>
+      </c>
+      <c r="C4" t="n">
+        <v>111643345</v>
+      </c>
+      <c r="D4" t="n">
+        <v>27</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
